--- a/post/causal/probs.xlsx
+++ b/post/causal/probs.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dimitris/Documents/work/website/current/content/post/causal/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E21C06EF-4883-3A4A-BBA7-26130FFB3DE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADD66394-6624-5E46-9585-5B4715655831}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19300" yWindow="900" windowWidth="10000" windowHeight="17500" xr2:uid="{B8C3A0B9-E39C-164C-A784-453520BF8C62}"/>
+    <workbookView xWindow="7360" yWindow="760" windowWidth="17460" windowHeight="18880" xr2:uid="{B8C3A0B9-E39C-164C-A784-453520BF8C62}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="16">
   <si>
     <t>E</t>
   </si>
@@ -58,7 +58,31 @@
     <t>P(H,E,C)</t>
   </si>
   <si>
-    <t>P(H|E,C) * P(C|E) * P(G)</t>
+    <t>P(H,C)</t>
+  </si>
+  <si>
+    <t>P(C)</t>
+  </si>
+  <si>
+    <t>P(H=1|C)</t>
+  </si>
+  <si>
+    <t>P(H=1|do(C))</t>
+  </si>
+  <si>
+    <t>Σ_E P(H,E,C)</t>
+  </si>
+  <si>
+    <t>Σ_H P(H,C)</t>
+  </si>
+  <si>
+    <t>P(H,C) / P(C)</t>
+  </si>
+  <si>
+    <t>Σ_E P(H|E,C) * P(E)</t>
+  </si>
+  <si>
+    <t>P(H|E,C) * P(C|E) * P(E)</t>
   </si>
 </sst>
 </file>
@@ -410,7 +434,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD73D522-4BA2-3A43-8A59-CCD427EF54AA}">
-  <dimension ref="A2:E24"/>
+  <dimension ref="A2:E44"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
@@ -420,7 +444,7 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="D3">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
@@ -516,7 +540,7 @@
         <v>6</v>
       </c>
       <c r="E15" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.2">
@@ -530,11 +554,11 @@
         <v>0</v>
       </c>
       <c r="D16">
-        <f>(1-$D$10)*(1-$D$6)*$D$3</f>
-        <v>0.47025</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+        <f>(1-$D$10)*(1-$D$6)*(1-$D$3)</f>
+        <v>0.84645000000000004</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>0</v>
       </c>
@@ -545,11 +569,11 @@
         <v>1</v>
       </c>
       <c r="D17">
-        <f>(1-$D$11)*$D$6*$D$3</f>
-        <v>4.9500000000000004E-3</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+        <f>(1-$D$11)*$D$6*(1-$D$3)</f>
+        <v>8.9100000000000013E-3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>0</v>
       </c>
@@ -561,10 +585,10 @@
       </c>
       <c r="D18">
         <f>(1-$D$12)*(1-$D$7)*$D$3</f>
-        <v>4.0000000000000036E-3</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
+        <v>8.000000000000008E-4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>0</v>
       </c>
@@ -576,10 +600,10 @@
       </c>
       <c r="D19">
         <f>(1-$D$13)*$D$7*$D$3</f>
-        <v>0.46529999999999999</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+        <v>9.3060000000000004E-2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>1</v>
       </c>
@@ -590,11 +614,11 @@
         <v>0</v>
       </c>
       <c r="D20">
-        <f>$D$10*(1-$D$6)*$D$3</f>
-        <v>2.4750000000000001E-2</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
+        <f>$D$10*(1-$D$6)*(1-$D$3)</f>
+        <v>4.4550000000000006E-2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>1</v>
       </c>
@@ -605,11 +629,11 @@
         <v>1</v>
       </c>
       <c r="D21">
-        <f>$D$11*$D$6*$D$3</f>
-        <v>5.0000000000000002E-5</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
+        <f>$D$11*$D$6*(1-$D$3)</f>
+        <v>9.0000000000000006E-5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>1</v>
       </c>
@@ -621,10 +645,10 @@
       </c>
       <c r="D22">
         <f>$D$12*(1-$D$7)*$D$3</f>
-        <v>1.0000000000000009E-3</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
+        <v>2.000000000000002E-4</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>1</v>
       </c>
@@ -636,13 +660,162 @@
       </c>
       <c r="D23">
         <f>$D$13*$D$7*$D$3</f>
-        <v>2.9699999999999997E-2</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
+        <v>5.94E-3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
       <c r="D24">
         <f>SUM(D16:D23)</f>
         <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>2</v>
+      </c>
+      <c r="C27" t="s">
+        <v>1</v>
+      </c>
+      <c r="D27" t="s">
+        <v>7</v>
+      </c>
+      <c r="E27" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A28">
+        <v>0</v>
+      </c>
+      <c r="C28">
+        <v>0</v>
+      </c>
+      <c r="D28">
+        <f>D16+D18</f>
+        <v>0.84725000000000006</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A29">
+        <v>0</v>
+      </c>
+      <c r="C29">
+        <v>1</v>
+      </c>
+      <c r="D29">
+        <f>D17+D19</f>
+        <v>0.10197000000000001</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A30">
+        <v>1</v>
+      </c>
+      <c r="C30">
+        <v>0</v>
+      </c>
+      <c r="D30">
+        <f>D20+D22</f>
+        <v>4.4750000000000005E-2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A31">
+        <v>1</v>
+      </c>
+      <c r="C31">
+        <v>1</v>
+      </c>
+      <c r="D31">
+        <f>D21+D23</f>
+        <v>6.0299999999999998E-3</v>
+      </c>
+    </row>
+    <row r="34" spans="3:5" x14ac:dyDescent="0.2">
+      <c r="C34" t="s">
+        <v>1</v>
+      </c>
+      <c r="D34" t="s">
+        <v>8</v>
+      </c>
+      <c r="E34" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="35" spans="3:5" x14ac:dyDescent="0.2">
+      <c r="C35">
+        <v>0</v>
+      </c>
+      <c r="D35">
+        <f>D28+D30</f>
+        <v>0.89200000000000002</v>
+      </c>
+    </row>
+    <row r="36" spans="3:5" x14ac:dyDescent="0.2">
+      <c r="C36">
+        <v>1</v>
+      </c>
+      <c r="D36">
+        <f>D29+D31</f>
+        <v>0.108</v>
+      </c>
+    </row>
+    <row r="38" spans="3:5" x14ac:dyDescent="0.2">
+      <c r="C38" t="s">
+        <v>1</v>
+      </c>
+      <c r="D38" t="s">
+        <v>9</v>
+      </c>
+      <c r="E38" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="39" spans="3:5" x14ac:dyDescent="0.2">
+      <c r="C39">
+        <v>0</v>
+      </c>
+      <c r="D39">
+        <f>D30/D35</f>
+        <v>5.0168161434977585E-2</v>
+      </c>
+    </row>
+    <row r="40" spans="3:5" x14ac:dyDescent="0.2">
+      <c r="C40">
+        <v>1</v>
+      </c>
+      <c r="D40">
+        <f>D31/D36</f>
+        <v>5.5833333333333332E-2</v>
+      </c>
+    </row>
+    <row r="42" spans="3:5" x14ac:dyDescent="0.2">
+      <c r="C42" t="s">
+        <v>1</v>
+      </c>
+      <c r="D42" t="s">
+        <v>10</v>
+      </c>
+      <c r="E42" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="43" spans="3:5" x14ac:dyDescent="0.2">
+      <c r="C43">
+        <v>0</v>
+      </c>
+      <c r="D43">
+        <f>D10*(1-D3)+D12*D3</f>
+        <v>6.5000000000000002E-2</v>
+      </c>
+    </row>
+    <row r="44" spans="3:5" x14ac:dyDescent="0.2">
+      <c r="C44">
+        <v>1</v>
+      </c>
+      <c r="D44">
+        <f>D11*(1-D3)+D13*D3</f>
+        <v>1.5000000000000001E-2</v>
       </c>
     </row>
   </sheetData>
